--- a/finance/农夫山泉/农夫山泉.xlsx
+++ b/finance/农夫山泉/农夫山泉.xlsx
@@ -1193,7 +1193,7 @@
       </c>
       <c r="B1" s="5" t="inlineStr">
         <is>
-          <t>扣非净利润（亿）</t>
+          <t>归母净利润(亿)</t>
         </is>
       </c>
       <c r="C1" s="5" t="inlineStr">
@@ -1228,10 +1228,10 @@
     </row>
     <row r="2">
       <c r="A2" s="15" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B2" s="15" t="n">
-        <v>121.23</v>
+        <v>158.68</v>
       </c>
       <c r="C2" s="8">
         <f>(B2-B3)/B3</f>
@@ -1239,11 +1239,11 @@
       </c>
       <c r="E2" s="15" t="inlineStr">
         <is>
-          <t>当年净利润</t>
+          <t>当年净利(2026E)</t>
         </is>
       </c>
       <c r="F2" s="15">
-        <f>B3</f>
+        <f>B2*(1+F3)</f>
         <v/>
       </c>
       <c r="G2" s="15" t="n"/>
@@ -1301,10 +1301,10 @@
     </row>
     <row r="3">
       <c r="A3" s="15" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B3" s="15" t="n">
-        <v>120.79</v>
+        <v>121.23</v>
       </c>
       <c r="C3" s="8">
         <f>(B3-B4)/B4</f>
@@ -1312,11 +1312,11 @@
       </c>
       <c r="E3" s="15" t="inlineStr">
         <is>
-          <t>预估增速</t>
+          <t>2026增速(2025高基数后温和外推)</t>
         </is>
       </c>
       <c r="F3" s="10" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="G3" s="10" t="n"/>
       <c r="H3" s="10" t="n"/>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="4">
       <c r="A4" s="15" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="B4" s="15" t="n">
-        <v>84.95</v>
+        <v>120.79</v>
       </c>
       <c r="C4" s="8">
         <f>(B4-B5)/B5</f>
@@ -1370,11 +1370,11 @@
       </c>
       <c r="E4" s="15" t="inlineStr">
         <is>
-          <t>净利润折扣</t>
+          <t>前瞻增速(2027-29)</t>
         </is>
       </c>
       <c r="F4" s="11" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="G4" s="11" t="n"/>
       <c r="H4" s="11" t="n"/>
@@ -1391,10 +1391,10 @@
     </row>
     <row r="5">
       <c r="A5" s="15" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="B5" s="15" t="n">
-        <v>71.62</v>
+        <v>84.95</v>
       </c>
       <c r="C5" s="8">
         <f>(B5-B6)/B6</f>
@@ -1402,12 +1402,11 @@
       </c>
       <c r="E5" s="15" t="inlineStr">
         <is>
-          <t>3年后净利润</t>
-        </is>
-      </c>
-      <c r="F5" s="15">
-        <f>F2*F4*(1+F3)*(1+F3)</f>
-        <v/>
+          <t>净利润折扣</t>
+        </is>
+      </c>
+      <c r="F5" s="15" t="n">
+        <v>1</v>
       </c>
       <c r="G5" s="15" t="n"/>
       <c r="H5" s="15" t="n"/>
@@ -1424,19 +1423,23 @@
     </row>
     <row r="6">
       <c r="A6" s="15" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="B6" s="15" t="n">
-        <v>52.77</v>
-      </c>
-      <c r="C6" s="8" t="n"/>
+        <v>71.62</v>
+      </c>
+      <c r="C6" s="8">
+        <f>(B6-B7)/B7</f>
+        <v/>
+      </c>
       <c r="E6" s="15" t="inlineStr">
         <is>
-          <t>合理pe(无风险收益率倒数)</t>
-        </is>
-      </c>
-      <c r="F6" s="11" t="n">
-        <v>27.5</v>
+          <t>3年后净利(2029)</t>
+        </is>
+      </c>
+      <c r="F6" s="11">
+        <f>F2*F5*(1+F4)^3</f>
+        <v/>
       </c>
       <c r="G6" s="11" t="n"/>
       <c r="H6" s="11" t="n"/>
@@ -1452,17 +1455,20 @@
       <c r="S6" s="27" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="n"/>
-      <c r="B7" s="15" t="n"/>
+      <c r="A7" s="15" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B7" s="15" t="n">
+        <v>52.77</v>
+      </c>
       <c r="C7" s="8" t="n"/>
       <c r="E7" s="15" t="inlineStr">
         <is>
-          <t>估计市值</t>
-        </is>
-      </c>
-      <c r="F7" s="15">
-        <f>F5*F6</f>
-        <v/>
+          <t>合理pe(=1/个人无风险利率3.6%)</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="n">
+        <v>27.5</v>
       </c>
       <c r="G7" s="15" t="n"/>
       <c r="H7" s="15" t="n"/>
@@ -1483,11 +1489,12 @@
       <c r="C8" s="8" t="n"/>
       <c r="E8" s="15" t="inlineStr">
         <is>
-          <t>安全边际</t>
-        </is>
-      </c>
-      <c r="F8" s="11" t="n">
-        <v>0.5</v>
+          <t>估计市值</t>
+        </is>
+      </c>
+      <c r="F8" s="11">
+        <f>F6*F7</f>
+        <v/>
       </c>
       <c r="G8" s="11" t="n"/>
       <c r="H8" s="11" t="n"/>
@@ -1508,12 +1515,11 @@
       <c r="C9" s="8" t="n"/>
       <c r="E9" s="15" t="inlineStr">
         <is>
-          <t>买点</t>
-        </is>
-      </c>
-      <c r="F9" s="15">
-        <f>F7*F8</f>
-        <v/>
+          <t>安全边际</t>
+        </is>
+      </c>
+      <c r="F9" s="15" t="n">
+        <v>0.5</v>
       </c>
       <c r="G9" s="15" t="n"/>
       <c r="H9" s="15" t="n"/>
@@ -1534,22 +1540,15 @@
       <c r="C10" s="8" t="n"/>
       <c r="E10" s="15" t="inlineStr">
         <is>
-          <t>卖点(50PE)</t>
+          <t>买点</t>
         </is>
       </c>
       <c r="F10" s="15">
-        <f>F5*50</f>
-        <v/>
-      </c>
-      <c r="G10" s="15" t="inlineStr">
-        <is>
-          <t>卖点(合理估值150%)</t>
-        </is>
-      </c>
-      <c r="H10" s="15">
-        <f>F7*1.5</f>
-        <v/>
-      </c>
+        <f>F8*F9</f>
+        <v/>
+      </c>
+      <c r="G10" s="15" t="n"/>
+      <c r="H10" s="15" t="n"/>
       <c r="J10" s="14" t="n"/>
       <c r="K10" s="25" t="n"/>
       <c r="L10" s="25" t="n"/>
@@ -1562,8 +1561,15 @@
       <c r="S10" s="27" t="n"/>
     </row>
     <row r="11">
-      <c r="E11" s="15" t="n"/>
-      <c r="F11" s="15" t="n"/>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>卖点一(当年×50PE)</t>
+        </is>
+      </c>
+      <c r="F11" s="15">
+        <f>F2*50</f>
+        <v/>
+      </c>
       <c r="G11" s="15" t="n"/>
       <c r="H11" s="15" t="n"/>
       <c r="J11" s="14" t="n"/>
@@ -1578,8 +1584,15 @@
       <c r="S11" s="27" t="n"/>
     </row>
     <row r="12">
-      <c r="E12" s="15" t="n"/>
-      <c r="F12" s="15" t="n"/>
+      <c r="E12" s="15" t="inlineStr">
+        <is>
+          <t>卖点二(当年×55PE)</t>
+        </is>
+      </c>
+      <c r="F12" s="15">
+        <f>F2*55</f>
+        <v/>
+      </c>
       <c r="G12" s="15" t="n"/>
       <c r="H12" s="15" t="n"/>
       <c r="J12" s="14" t="n"/>
@@ -1594,6 +1607,15 @@
       <c r="S12" s="27" t="n"/>
     </row>
     <row r="13">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>卖点三(当年×60PE)</t>
+        </is>
+      </c>
+      <c r="F13">
+        <f>F2*60</f>
+        <v/>
+      </c>
       <c r="J13" s="14" t="n"/>
       <c r="K13" s="25" t="n"/>
       <c r="L13" s="25" t="n"/>

--- a/finance/农夫山泉/农夫山泉.xlsx
+++ b/finance/农夫山泉/农夫山泉.xlsx
@@ -1312,11 +1312,11 @@
       </c>
       <c r="E3" s="15" t="inlineStr">
         <is>
-          <t>2026增速(2025高基数后温和外推)</t>
+          <t>2026增速(用户拍板·茶减速保守档)</t>
         </is>
       </c>
       <c r="F3" s="10" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="G3" s="10" t="n"/>
       <c r="H3" s="10" t="n"/>
@@ -1374,7 +1374,7 @@
         </is>
       </c>
       <c r="F4" s="11" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="G4" s="11" t="n"/>
       <c r="H4" s="11" t="n"/>
